--- a/jpcore-r4b/develop/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-careplan.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-careplan.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -371,7 +371,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -510,7 +510,7 @@
     <t>CarePlan.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|Measure|ActivityDefinition|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.3.0|Questionnaire|4.3.0|Measure|4.3.0|ActivityDefinition|4.3.0|OperationDefinition|4.3.0)
 </t>
   </si>
   <si>
@@ -681,7 +681,7 @@
     <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-category</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-category|4.3.0</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -870,7 +870,7 @@
     <t>CarePlan.careTeam</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam)
+    <t xml:space="preserve">Reference(CareTeam|4.3.0)
 </t>
   </si>
   <si>
@@ -923,7 +923,7 @@
     <t>CarePlan.supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.3.0)
 </t>
   </si>
   <si>
@@ -945,7 +945,7 @@
     <t>CarePlan.goal</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Goal)
+    <t xml:space="preserve">Reference(Goal|4.3.0)
 </t>
   </si>
   <si>
@@ -1050,7 +1050,7 @@
     <t>Identifies the results of the activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.3.0</t>
   </si>
   <si>
     <t>CarePlan.activity.outcomeReference</t>
@@ -1178,7 +1178,7 @@
     <t>CarePlan.activity.detail.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Questionnaire|Measure|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.3.0|ActivityDefinition|4.3.0|Questionnaire|4.3.0|Measure|4.3.0|OperationDefinition|4.3.0)
 </t>
   </si>
   <si>
@@ -1212,7 +1212,7 @@
     <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.3.0</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1239,7 +1239,7 @@
     <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.3.0</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1369,7 +1369,7 @@
     <t>CarePlan.activity.detail.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.3.0)
 </t>
   </si>
   <si>
@@ -1432,7 +1432,7 @@
     <t>A product supplied or administered as part of a care plan activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.3.0</t>
   </si>
   <si>
     <t>.participation[typeCode=PRD].role</t>
@@ -1448,7 +1448,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.3.0}
 </t>
   </si>
   <si>
@@ -1813,17 +1813,17 @@
   <dimension ref="A1:AN61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.58203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.58203125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="235.01953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1832,26 +1832,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="159.0703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.859375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="42.671875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="136.375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.24609375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.58203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="55.8046875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="173.13671875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="145.83984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="47.84375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="148.43359375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="125.03125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-careplan.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-careplan.xlsx
@@ -266,14 +266,14 @@
 </t>
   </si>
   <si>
-    <t>Healthcare plan for patient or group</t>
-  </si>
-  <si>
-    <t>Describes the intention of how one or more practitioners intend to deliver care for a particular patient, group or community for a period of time, possibly limited to care for a specific condition or set of conditions.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>患者またはグループの健康計画 / Healthcare plan for patient or group</t>
+  </si>
+  <si>
+    <t>1人または複数の医療従事者が特定の患者、グループ、またはコミュニティに一定期間ケアを提供する意図を述べ、特定の状態または一連の状態に限定される場合がある。 / Describes the intention of how one or more practitioners intend to deliver care for a particular patient, group or community for a period of time, possibly limited to care for a specific condition or set of conditions.</t>
+  </si>
+  <si>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -298,13 +298,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -317,16 +317,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -337,13 +337,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -356,19 +356,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>人間の言語。 / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -388,13 +388,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト要約 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -414,19 +414,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>含まれている、インラインのリソース / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -444,33 +444,33 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>CarePlan.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張により、安全に無視できない拡張を、安全に無視できる大多数の拡張と明確に区別することができます。これにより、実装者が拡張の存在を禁止する必要がなくなり、相互運用性が促進されます。詳細については、[修飾子拡張の定義](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension)を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -483,16 +483,16 @@
 </t>
   </si>
   <si>
-    <t>External Ids for this plan</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this care plan by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the care plan as it is known by various participating systems and in a way that remains consistent across servers.</t>
+    <t>このプランの外部ID / External Ids for this plan</t>
+  </si>
+  <si>
+    <t>パフォーマーまたはその他のシステムによって割り当てられたこのケアプランのビジネスidentifierは、リソースが更新され、サーバからサーバへ伝播する際に一定のままであります。 / Business identifiers assigned to this care plan by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません（[discussion]（resource.html＃identifiers）を参照）。 identifierが単一のリソースインスタンスにのみ表示されることが最善の方法ですが、ビジネス上の実践によっては、同じidentifierを持つ複数のリソースインスタンスが存在する場合があります。 たとえば、複数の患者と個人リソースインスタンスが同じ社会保険番号を共有する場合があります。 / This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>様々な参加システムで知られているケアプランの識別を可能にし、サーバー間で一貫した方法を維持する。 / Allows identification of the care plan as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -514,10 +514,10 @@
 </t>
   </si>
   <si>
-    <t>Instantiates FHIR protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan.</t>
+    <t>FHIRプロトコルまたは定義をインスタンス化します。 / Instantiates FHIR protocol or definition</t>
+  </si>
+  <si>
+    <t>このCarePlanで全体または一部に従われるFHIRで定義されたプロトコル、ガイドライン、アンケートなどの定義を指すURL。 / The URL pointing to a FHIR-defined protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan.</t>
   </si>
   <si>
     <t>Request.instantiatesCanonical</t>
@@ -529,13 +529,13 @@
     <t>CarePlan.instantiatesUri</t>
   </si>
   <si>
-    <t>Instantiates external protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan.</t>
-  </si>
-  <si>
-    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+    <t>外部プロトコルまたは定義を実体化する。 / Instantiates external protocol or definition</t>
+  </si>
+  <si>
+    <t>このCarePlanが全体または一部に従っている外部管理プロトコル、ガイドライン、アンケート、または他の定義を指すURL。 / The URL pointing to an externally maintained protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan.</t>
+  </si>
+  <si>
+    <t>これはHTMLページ、PDFなどであるか、解決不能なURIidentifierである可能性があります。 / This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
   </si>
   <si>
     <t>Request.instantiatesUri</t>
@@ -552,13 +552,13 @@
 </t>
   </si>
   <si>
-    <t>Fulfills CarePlan</t>
-  </si>
-  <si>
-    <t>A care plan that is fulfilled in whole or in part by this care plan.</t>
-  </si>
-  <si>
-    <t>Allows tracing of the care plan and tracking whether proposals/recommendations were acted upon.</t>
+    <t>ケアプランを実行する / Fulfills CarePlan</t>
+  </si>
+  <si>
+    <t>このケアプランによって全体または一部が満たされるケアプラン。 / A care plan that is fulfilled in whole or in part by this care plan.</t>
+  </si>
+  <si>
+    <t>ケアプランの追跡と、提案/推奨事項が実行されたかどうかの追跡を可能にする。 / Allows tracing of the care plan and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
     <t>Request.basedOn</t>
@@ -571,16 +571,16 @@
 </t>
   </si>
   <si>
-    <t>CarePlan replaced by this CarePlan</t>
-  </si>
-  <si>
-    <t>Completed or terminated care plan whose function is taken by this new care plan.</t>
-  </si>
-  <si>
-    <t>The replacement could be because the initial care plan was immediately rejected (due to an issue) or because the previous care plan was completed, but the need for the action described by the care plan remains ongoing.</t>
-  </si>
-  <si>
-    <t>Allows tracing the continuation of a therapy or administrative process instantiated through multiple care plans.</t>
+    <t>このCarePlanで以前のCarePlanが入れ替わりました。 / CarePlan replaced by this CarePlan</t>
+  </si>
+  <si>
+    <t>この新しい介護計画によって機能が引き継がれた完了または終了した介護計画。 / Completed or terminated care plan whose function is taken by this new care plan.</t>
+  </si>
+  <si>
+    <t>置き換えは、最初の介護計画が即座に拒否されたためか（何か問題があったため）前の介護計画が完了したが、介護計画で説明されたアクションのニーズが継続しているためかもしれません。 / The replacement could be because the initial care plan was immediately rejected (due to an issue) or because the previous care plan was completed, but the need for the action described by the care plan remains ongoing.</t>
+  </si>
+  <si>
+    <t>複数のケアプランを通じてインスタンス化された治療または管理プロセスの継続を追跡できるようにする。 / Allows tracing the continuation of a therapy or administrative process instantiated through multiple care plans.</t>
   </si>
   <si>
     <t>Request.replaces</t>
@@ -589,29 +589,30 @@
     <t>CarePlan.partOf</t>
   </si>
   <si>
-    <t>Part of referenced CarePlan</t>
-  </si>
-  <si>
-    <t>A larger care plan of which this particular care plan is a component or step.</t>
-  </si>
-  <si>
-    <t>Each care plan is an independent request, such that having a care plan be part of another care plan can cause issues with cascading statuses.  As such, this element is still being discussed.</t>
+    <t>参照されたCarePlanの一部 / Part of referenced CarePlan</t>
+  </si>
+  <si>
+    <t>この特定の介護計画が構成要素またはステップである、より大規模な介護計画 / A larger care plan of which this particular care plan is a component or step.</t>
+  </si>
+  <si>
+    <t>それぞれのケアプランは独立したリクエストであり、他のケアプランの一部になることが問題を引き起こすことがあるため、この要素についてはまだ議論中です。 / Each care plan is an independent request, such that having a care plan be part of another care plan can cause issues with cascading statuses.  As such, this element is still being discussed.</t>
   </si>
   <si>
     <t>CarePlan.status</t>
   </si>
   <si>
-    <t>draft | active | on-hold | revoked | completed | entered-in-error | unknown</t>
-  </si>
-  <si>
-    <t>Indicates whether the plan is currently being acted upon, represents future intentions or is now a historical record.</t>
-  </si>
-  <si>
-    <t>The unknown code is not to be used to convey other statuses.  The unknown code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the care plan.
+    <t>下書き| アクティブ| 保留中| 取り消された| 完了 | エラー入力| 不明 / draft | active | on-hold | revoked | completed | entered-in-error | unknown</t>
+  </si>
+  <si>
+    <t>計画が実行中か、将来の意図を表しているか、現在歴史的記録であるかを示します。 / Indicates whether the plan is currently being acted upon, represents future intentions or is now a historical record.</t>
+  </si>
+  <si>
+    <t>未知のコードは、他のステータスを伝えるために使用されるべきではありません。未知のコードは、ステータスの1つが適用されるときに使用されるべきですが、作成システムがケアプランの現在の状態を知らない場合にも使用されます。
+この要素は、プランが現在有効でないことを示す入力エラーのコードを含むステータスを含んでいるため、修飾子としてラベル付けされます。 / The unknown code is not to be used to convey other statuses.  The unknown code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the care plan.
 This element is labeled as a modifier because the status contains the code entered-in-error that marks the plan as not currently valid.</t>
   </si>
   <si>
-    <t>Allows clinicians to determine whether the plan is actionable or not.</t>
+    <t>臨床医がプランが実行可能かどうかを判断できるようにする。 / Allows clinicians to determine whether the plan is actionable or not.</t>
   </si>
   <si>
     <t>required</t>
@@ -635,19 +636,19 @@
     <t>CarePlan.intent</t>
   </si>
   <si>
-    <t>proposal | plan | order | option</t>
-  </si>
-  <si>
-    <t>Indicates the level of authority/intentionality associated with the care plan and where the care plan fits into the workflow chain.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
-  </si>
-  <si>
-    <t>Proposals/recommendations, plans and orders all use the same structure and can exist in the same fulfillment chain.</t>
-  </si>
-  <si>
-    <t>Codes indicating the degree of authority/intentionality associated with a care plan.</t>
+    <t>提案 | 計画 | 注文 | オプション / proposal | plan | order | option</t>
+  </si>
+  <si>
+    <t>ケアプランに関連する権限/意図のレベルを示し、ケアプランがワークフローチェーンにどのようにフィットするかを示します。 / Indicates the level of authority/intentionality associated with the care plan and where the care plan fits into the workflow chain.</t>
+  </si>
+  <si>
+    <t>この要素は修飾子としてラベル付けされています。なぜなら、意図が変わり、リソースが実際に適用可能な場合と方法が変わるからです。 / This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
+  </si>
+  <si>
+    <t>提案/推奨事項、計画、およびオーダーはすべて同じ構造を使用し、同じ履行チェーンに存在できる。 / Proposals/recommendations, plans and orders all use the same structure and can exist in the same fulfillment chain.</t>
+  </si>
+  <si>
+    <t>看護計画に関連する権限/意図の程度を示すコード / Codes indicating the degree of authority/intentionality associated with a care plan.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/care-plan-intent|4.3.0</t>
@@ -663,22 +664,22 @@
 </t>
   </si>
   <si>
-    <t>Type of plan</t>
-  </si>
-  <si>
-    <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", "wellness plan", etc.</t>
-  </si>
-  <si>
-    <t>There may be multiple axes of categorization and one plan may serve multiple purposes.  In some cases, this may be redundant with references to CarePlan.concern.</t>
-  </si>
-  <si>
-    <t>Used for filtering what plan(s) are retrieved and displayed to different types of users.</t>
+    <t>プランの種類 / Type of plan</t>
+  </si>
+  <si>
+    <t>複数の共存する計画間の差別化をサポートするための「種類」の計画を識別します；例えば「在宅医療」「精神科」「喘息」「疾患管理」「ウェルネスプラン」など。 / Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", "wellness plan", etc.</t>
+  </si>
+  <si>
+    <t>複数の分類軸が存在し、1つの計画が複数の目的に役立つことがあります。場合によっては、これはCarePlan.concernへの参照と重複する場合があります。 / There may be multiple axes of categorization and one plan may serve multiple purposes.  In some cases, this may be redundant with references to CarePlan.concern.</t>
+  </si>
+  <si>
+    <t>異なるタイプのユーザーに取得・表示されるプランをフィルタリングするために使用される。 / Used for filtering what plan(s) are retrieved and displayed to different types of users.</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", etc.</t>
+    <t>「これが複数存在する計画の区別を支援するための「種類」の計画である」（たとえば、「在宅医療」、「精神医療」、「喘息」、「疾患管理」など）。 / Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", etc.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/care-plan-category|4.3.0</t>
@@ -694,22 +695,22 @@
 </t>
   </si>
   <si>
-    <t>Human-friendly name for the care plan</t>
-  </si>
-  <si>
-    <t>Human-friendly name for the care plan.</t>
+    <t>ケアプランに対する人間に優しい名前 / Human-friendly name for the care plan</t>
+  </si>
+  <si>
+    <t>介護計画のための人間にやさしい名前。 / Human-friendly name for the care plan.</t>
   </si>
   <si>
     <t>CarePlan.description</t>
   </si>
   <si>
-    <t>Summary of nature of plan</t>
-  </si>
-  <si>
-    <t>A description of the scope and nature of the plan.</t>
-  </si>
-  <si>
-    <t>Provides more detail than conveyed by category.</t>
+    <t>計画の性質の要約 / Summary of nature of plan</t>
+  </si>
+  <si>
+    <t>計画の範囲と性質の説明。 / A description of the scope and nature of the plan.</t>
+  </si>
+  <si>
+    <t>カテゴリで伝えられるよりも詳細な情報を提供する。 / Provides more detail than conveyed by category.</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
@@ -726,10 +727,10 @@
 </t>
   </si>
   <si>
-    <t>Who the care plan is for</t>
-  </si>
-  <si>
-    <t>Identifies the patient or group whose intended care is described by the plan.</t>
+    <t>ケアプランの対象者は誰ですか？ / Who the care plan is for</t>
+  </si>
+  <si>
+    <t>計画に記載されている患者またはグループを特定します。 / Identifies the patient or group whose intended care is described by the plan.</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -751,13 +752,13 @@
 </t>
   </si>
   <si>
-    <t>Encounter created as part of</t>
-  </si>
-  <si>
-    <t>The Encounter during which this CarePlan was created or to which the creation of this record is tightly associated.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. CarePlan activities conducted as a result of the care plan may well occur as part of other encounters.</t>
+    <t>一部として作成された受療行動 / Encounter created as part of</t>
+  </si>
+  <si>
+    <t>このCarePlanが作成された受療行動、またはこの記録の作成に密接に関係する受療行動。 / The Encounter during which this CarePlan was created or to which the creation of this record is tightly associated.</t>
+  </si>
+  <si>
+    <t>これは通常、イベントが発生したエンカウンター内で行われますが、公式的なエンカウンターの完了前または後でも、エンカウンターの文脈に関連するアクティビティが開始される場合があります。 ケアプランに従って実施されるケアプランアクティビティは、他のエンカウンターの一部として行われる可能性があります。 / This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. CarePlan activities conducted as a result of the care plan may well occur as part of other encounters.</t>
   </si>
   <si>
     <t>Request.context</t>
@@ -783,16 +784,16 @@
 </t>
   </si>
   <si>
-    <t>Time period plan covers</t>
-  </si>
-  <si>
-    <t>Indicates when the plan did (or is intended to) come into effect and end.</t>
-  </si>
-  <si>
-    <t>Any activities scheduled as part of the plan should be constrained to the specified period regardless of whether the activities are planned within a single encounter/episode or across multiple encounters/episodes (e.g. the longitudinal management of a chronic condition).</t>
-  </si>
-  <si>
-    <t>Allows tracking what plan(s) are in effect at a particular time.</t>
+    <t>時間期間プランがカバーされています / Time period plan covers</t>
+  </si>
+  <si>
+    <t>計画が（実行される予定である）開始時期と終了時期を示します。 / Indicates when the plan did (or is intended to) come into effect and end.</t>
+  </si>
+  <si>
+    <t>計画の一部として予定された任意のアクティビティは、単一のエンカウンタ/エピソード内で計画されたものであるか、複数のエンカウンタ/エピソードにわたって計画されたものであるかに関係なく、指定された期間内に制約される必要があります（例えば、慢性疾患の長期管理）。 / Any activities scheduled as part of the plan should be constrained to the specified period regardless of whether the activities are planned within a single encounter/episode or across multiple encounters/episodes (e.g. the longitudinal management of a chronic condition).</t>
+  </si>
+  <si>
+    <t>特定の時点でどのプランが有効であるかを追跡できるようにする。 / Allows tracking what plan(s) are in effect at a particular time.</t>
   </si>
   <si>
     <t>Request.occurrence[x]</t>
@@ -818,10 +819,10 @@
 </t>
   </si>
   <si>
-    <t>Date record was first recorded</t>
-  </si>
-  <si>
-    <t>Represents when this particular CarePlan record was created in the system, which is often a system-generated date.</t>
+    <t>日付記録が最初に記録された。 / Date record was first recorded</t>
+  </si>
+  <si>
+    <t>これは特定のCarePlanレコードがシステム内で作成された日を表します。これはしばしばシステムが生成した日付です。 / Represents when this particular CarePlan record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
     <t>Request.authoredOn</t>
@@ -840,13 +841,13 @@
 </t>
   </si>
   <si>
-    <t>Who is the designated responsible party</t>
-  </si>
-  <si>
-    <t>When populated, the author is responsible for the care plan.  The care plan is attributed to the author.</t>
-  </si>
-  <si>
-    <t>The author may also be a contributor.  For example, an organization can be an author, but not listed as a contributor.</t>
+    <t>指名された責任者は誰ですか？ / Who is the designated responsible party</t>
+  </si>
+  <si>
+    <t>人口密集地において、著者はケアプランに責任を持っています。ケアプランは著者に帰属されます。 / When populated, the author is responsible for the care plan.  The care plan is attributed to the author.</t>
+  </si>
+  <si>
+    <t>著者は寄稿者でもある可能性があります。例えば、組織は著者として表示されますが、寄稿者としては表示されません。 / The author may also be a contributor.  For example, an organization can be an author, but not listed as a contributor.</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -858,13 +859,13 @@
     <t>CarePlan.contributor</t>
   </si>
   <si>
-    <t>Who provided the content of the care plan</t>
-  </si>
-  <si>
-    <t>Identifies the individual(s) or organization who provided the contents of the care plan.</t>
-  </si>
-  <si>
-    <t>Collaborative care plans may have multiple contributors.</t>
+    <t>誰がケアプランの内容を提供しましたか？ / Who provided the content of the care plan</t>
+  </si>
+  <si>
+    <t>介護プランの内容を提供した個人または組織を特定する。 / Identifies the individual(s) or organization who provided the contents of the care plan.</t>
+  </si>
+  <si>
+    <t>共同ケアプランには複数の貢献者がいる場合があります。 / Collaborative care plans may have multiple contributors.</t>
   </si>
   <si>
     <t>CarePlan.careTeam</t>
@@ -874,13 +875,13 @@
 </t>
   </si>
   <si>
-    <t>Who's involved in plan?</t>
-  </si>
-  <si>
-    <t>Identifies all people and organizations who are expected to be involved in the care envisioned by this plan.</t>
-  </si>
-  <si>
-    <t>Allows representation of care teams, helps scope care plan.  In some cases may be a determiner of access permissions.</t>
+    <t>この計画に誰が関わっているのですか？ / Who's involved in plan?</t>
+  </si>
+  <si>
+    <t>この計画によって想定されるケアに関与するすべての人々や組織を特定する。 / Identifies all people and organizations who are expected to be involved in the care envisioned by this plan.</t>
+  </si>
+  <si>
+    <t>ケアチームの表現を可能にし、ケアプランの範囲を定めるのに役立つ。場合によってはアクセス権限の決定要因となることがある。 / Allows representation of care teams, helps scope care plan.  In some cases may be a determiner of access permissions.</t>
   </si>
   <si>
     <t>Request.performer {similar but does not entail CareTeam}</t>
@@ -896,16 +897,16 @@
 </t>
   </si>
   <si>
-    <t>Health issues this plan addresses</t>
-  </si>
-  <si>
-    <t>Identifies the conditions/problems/concerns/diagnoses/etc. whose management and/or mitigation are handled by this plan.</t>
-  </si>
-  <si>
-    <t>When the diagnosis is related to an allergy or intolerance, the Condition and AllergyIntolerance resources can both be used. However, to be actionable for decision support, using Condition alone is not sufficient as the allergy or intolerance condition needs to be represented as an AllergyIntolerance.</t>
-  </si>
-  <si>
-    <t>Links plan to the conditions it manages.  The element can identify risks addressed by the plan as well as active conditions.  (The Condition resource can include things like "at risk for hypertension" or "fall risk".)  Also scopes plans - multiple plans may exist addressing different concerns.</t>
+    <t>この計画が対処する健康上の問題 / Health issues this plan addresses</t>
+  </si>
+  <si>
+    <t>この計画で管理および軽減の対象となる状況、問題、懸念、診断等を特定する。 / Identifies the conditions/problems/concerns/diagnoses/etc. whose management and/or mitigation are handled by this plan.</t>
+  </si>
+  <si>
+    <t>診断がアレルギーまたは不耐症に関連している場合、ConditionおよびAllergyIntoleranceリソースの両方を使用できます。ただし、意思決定のサポートに有用であるためには、Conditionだけで十分ではなく、アレルギーまたは不耐症の状態をAllergyIntoleranceとして表現する必要があります。 / When the diagnosis is related to an allergy or intolerance, the Condition and AllergyIntolerance resources can both be used. However, to be actionable for decision support, using Condition alone is not sufficient as the allergy or intolerance condition needs to be represented as an AllergyIntolerance.</t>
+  </si>
+  <si>
+    <t>プランが管理する状態にプランをリンクする。この要素はプランが対処するリスクやアクティブな状態を識別できる。（Conditionリソースには「高血圧リスク」や「転倒リスク」などを含めることができる。）また、プランの範囲を定める - 異なる問題に対処する複数のプランが存在する場合がある。 / Links plan to the conditions it manages.  The element can identify risks addressed by the plan as well as active conditions.  (The Condition resource can include things like "at risk for hypertension" or "fall risk".)  Also scopes plans - multiple plans may exist addressing different concerns.</t>
   </si>
   <si>
     <t>Request.reasonReference</t>
@@ -927,16 +928,16 @@
 </t>
   </si>
   <si>
-    <t>Information considered as part of plan</t>
-  </si>
-  <si>
-    <t>Identifies portions of the patient's record that specifically influenced the formation of the plan.  These might include comorbidities, recent procedures, limitations, recent assessments, etc.</t>
-  </si>
-  <si>
-    <t>Use "concern" to identify specific conditions addressed by the care plan.</t>
-  </si>
-  <si>
-    <t>Identifies barriers and other considerations associated with the care plan.</t>
+    <t>計画の一部として考慮される情報 / Information considered as part of plan</t>
+  </si>
+  <si>
+    <t>計画の形成に特定に影響を与えた患者の記録の部分を特定します。これらには、共存疾患、最近の手術、制限、最近の評価などが含まれます。 / Identifies portions of the patient's record that specifically influenced the formation of the plan.  These might include comorbidities, recent procedures, limitations, recent assessments, etc.</t>
+  </si>
+  <si>
+    <t>ケアプランで取り扱われる特定の状態を識別するために"concern"を使用してください。 / Use "concern" to identify specific conditions addressed by the care plan.</t>
+  </si>
+  <si>
+    <t>ケアプランに関連する障壁やその他の考慮事項を特定する。 / Identifies barriers and other considerations associated with the care plan.</t>
   </si>
   <si>
     <t>Request.supportingInfo</t>
@@ -949,16 +950,16 @@
 </t>
   </si>
   <si>
-    <t>Desired outcome of plan</t>
-  </si>
-  <si>
-    <t>Describes the intended objective(s) of carrying out the care plan.</t>
-  </si>
-  <si>
-    <t>Goal can be achieving a particular change or merely maintaining a current state or even slowing a decline.</t>
-  </si>
-  <si>
-    <t>Provides context for plan.  Allows plan effectiveness to be evaluated by clinicians.</t>
+    <t>計画の望まれる結果 / Desired outcome of plan</t>
+  </si>
+  <si>
+    <t>介護計画を実行することで意図される目標を説明する。 / Describes the intended objective(s) of carrying out the care plan.</t>
+  </si>
+  <si>
+    <t>目標は特定の変化を達成することであったり、現状を維持することであったり、衰退を遅らせることであることもある。 / Goal can be achieving a particular change or merely maintaining a current state or even slowing a decline.</t>
+  </si>
+  <si>
+    <t>プランのコンテキストを提供する。臨床医によるプランの有効性の評価を可能にする。 / Provides context for plan.  Allows plan effectiveness to be evaluated by clinicians.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode&lt;=OBJ].</t>
@@ -974,17 +975,17 @@
 </t>
   </si>
   <si>
-    <t>Action to occur as part of plan</t>
-  </si>
-  <si>
-    <t>Identifies a planned action to occur as part of the plan.  For example, a medication to be used, lab tests to perform, self-monitoring, education, etc.</t>
-  </si>
-  <si>
-    <t>Allows systems to prompt for performance of planned activities, and validate plans against best practice.</t>
-  </si>
-  <si>
-    <t>cpl-3:Provide a reference or detail, not both {detail.empty() or reference.empty()}
-ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}</t>
+    <t>計画の一環として発生する行動 / Action to occur as part of plan</t>
+  </si>
+  <si>
+    <t>計画の一部として発生する予定の行動を識別します。例えば、使用する薬、実施する実験、自己モニタリング、教育などがあります。 / Identifies a planned action to occur as part of the plan.  For example, a medication to be used, lab tests to perform, self-monitoring, education, etc.</t>
+  </si>
+  <si>
+    <t>計画されたアクティビティの実行を促し、ベストプラクティスに対してプランを検証することをシステムに可能にする。 / Allows systems to prompt for performance of planned activities, and validate plans against best practice.</t>
+  </si>
+  <si>
+    <t>cpl-3:参照文献または詳細を提供してください。両方は不要です。 / Provide a reference or detail, not both {detail.empty() or reference.empty()}
+ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}</t>
   </si>
   <si>
     <t>{no mapping
@@ -997,10 +998,10 @@
     <t>CarePlan.activity.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -1012,7 +1013,7 @@
     <t>CarePlan.activity.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1025,10 +1026,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1038,16 +1040,16 @@
     <t>CarePlan.activity.outcomeCodeableConcept</t>
   </si>
   <si>
-    <t>Results of the activity</t>
-  </si>
-  <si>
-    <t>Identifies the outcome at the point when the status of the activity is assessed.  For example, the outcome of an education activity could be patient understands (or not).</t>
-  </si>
-  <si>
-    <t>Note that this should not duplicate the activity status (e.g. completed or in progress).</t>
-  </si>
-  <si>
-    <t>Identifies the results of the activity.</t>
+    <t>活動の結果 / Results of the activity</t>
+  </si>
+  <si>
+    <t>活動の状況が評価された時点での結果を特定します。例えば、教育活動の結果は患者が理解したかどうかです。 / Identifies the outcome at the point when the status of the activity is assessed.  For example, the outcome of an education activity could be patient understands (or not).</t>
+  </si>
+  <si>
+    <t>これは活動の状態を複製してはいけないことに注意して下さい（例えば、完了したものや進行中のものなど）。 / Note that this should not duplicate the activity status (e.g. completed or in progress).</t>
+  </si>
+  <si>
+    <t>活動の結果を特定します。 / Identifies the results of the activity.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.3.0</t>
@@ -1056,16 +1058,16 @@
     <t>CarePlan.activity.outcomeReference</t>
   </si>
   <si>
-    <t>Appointment, Encounter, Procedure, etc.</t>
-  </si>
-  <si>
-    <t>Details of the outcome or action resulting from the activity.  The reference to an "event" resource, such as Procedure or Encounter or Observation, is the result/outcome of the activity itself.  The activity can be conveyed using CarePlan.activity.detail OR using the CarePlan.activity.reference (a reference to a “request” resource).</t>
-  </si>
-  <si>
-    <t>The activity outcome is independent of the outcome of the related goal(s).  For example, if the goal is to achieve a target body weight of 150 lbs and an activity is defined to diet, then the activity outcome could be calories consumed whereas the goal outcome is an observation for the actual body weight measured.</t>
-  </si>
-  <si>
-    <t>Links plan to resulting actions.</t>
+    <t>予約、受療行動、手続きなど。 / Appointment, Encounter, Procedure, etc.</t>
+  </si>
+  <si>
+    <t>アクティビティによって生じる結果や行動の詳細。プロシジャー（処置等）、エンカウンター、観察などの「イベント」リソースに参照していることは、アクティビティそのものの結果/成果です。CarePlan.activity.detailを使用するか、CarePlan.activity.reference（「リクエスト」リソースへの参照）を使用してアクティビティを伝えることができます。 / Details of the outcome or action resulting from the activity.  The reference to an "event" resource, such as Procedure or Encounter or Observation, is the result/outcome of the activity itself.  The activity can be conveyed using CarePlan.activity.detail OR using the CarePlan.activity.reference (a reference to a “request” resource).</t>
+  </si>
+  <si>
+    <t>活動の結果は、関連する目標の結果に独立しています。例えば、目標が体重150ポンドの達成であり、活動がダイエットと定義されている場合、活動の結果は消費カロリーであり、目標の結果は実際の体重の観察です。 / The activity outcome is independent of the outcome of the related goal(s).  For example, if the goal is to achieve a target body weight of 150 lbs and an activity is defined to diet, then the activity outcome could be calories consumed whereas the goal outcome is an observation for the actual body weight measured.</t>
+  </si>
+  <si>
+    <t>プランを結果のアクションにリンクする。 / Links plan to resulting actions.</t>
   </si>
   <si>
     <t>{Event that is outcome of Request in activity.reference}</t>
@@ -1081,16 +1083,16 @@
 </t>
   </si>
   <si>
-    <t>Comments about the activity status/progress</t>
-  </si>
-  <si>
-    <t>Notes about the adherence/status/progress of the activity.</t>
-  </si>
-  <si>
-    <t>This element should NOT be used to describe the activity to be performed - that occurs either within the resource pointed to by activity.detail.reference or in activity.detail.description.</t>
-  </si>
-  <si>
-    <t>Can be used to capture information about adherence, progress, concerns, etc.</t>
+    <t>活動状況/進捗についてのコメント / Comments about the activity status/progress</t>
+  </si>
+  <si>
+    <t>活動の遵守状況や進捗についてのメモ / Notes about the adherence/status/progress of the activity.</t>
+  </si>
+  <si>
+    <t>この要素は、実行されるアクティビティを説明するために使用しないでください。アクティビティの詳細な参照先のリソース内で行われるか、アクティビティの詳細説明に記載されます。 / This element should NOT be used to describe the activity to be performed - that occurs either within the resource pointed to by activity.detail.reference or in activity.detail.description.</t>
+  </si>
+  <si>
+    <t>アドヒアランス、進捗、懸念事項などに関する情報を記録するために使用できる。 / Can be used to capture information about adherence, progress, concerns, etc.</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="annotation"].value</t>
@@ -1106,17 +1108,17 @@
 </t>
   </si>
   <si>
-    <t>Activity details defined in specific resource</t>
-  </si>
-  <si>
-    <t>The details of the proposed activity represented in a specific resource.</t>
-  </si>
-  <si>
-    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4B/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  +    <t>特定のリソースで定義された活動の詳細 / Activity details defined in specific resource</t>
+  </si>
+  <si>
+    <t>特定のリソースに表現された提案された活動の詳細。 / The details of the proposed activity represented in a specific resource.</t>
+  </si>
+  <si>
+    <t>標準拡張機能が存在します（[リソースが目標に関連する]（extension-resource-pertainstogoal.html）），これにより、CarePlan.activity.referenceのいずれかの参照リソースから目標を参照できます。 CarePlanから独立して表示される場合には、CarePlan.activity.referenceによって参照されたリソースが表示される場合に目標が表示される必要があります。 この要素を使用して指示されたCarePlanを指すリクエストは、「basedOn」要素を使用してこのCarePlanを指すべきではありません。つまり、CarePlanの一部である要求はCarePlanに基づいていません。 / Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4B/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.   The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
   </si>
   <si>
-    <t>Details in a form consistent with other applications and contexts of use.</t>
+    <t>他のアプリケーションおよび使用コンテキストと一貫した形式の詳細。 / Details in a form consistent with other applications and contexts of use.</t>
   </si>
   <si>
     <t xml:space="preserve">cpl-3
@@ -1129,16 +1131,16 @@
     <t>CarePlan.activity.detail</t>
   </si>
   <si>
-    <t>In-line definition of activity</t>
-  </si>
-  <si>
-    <t>A simple summary of a planned activity suitable for a general care plan system (e.g. form driven) that doesn't know about specific resources such as procedure etc.</t>
-  </si>
-  <si>
-    <t>Details in a simple form for generic care plan systems.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>アクティビティのインライン定義 / In-line definition of activity</t>
+  </si>
+  <si>
+    <t>プロシジャー（処置等）など具体的なリソースを持たない一般介護プランシステム（フォーム駆動型など）に適した計画された活動の簡単な概要 / A simple summary of a planned activity suitable for a general care plan system (e.g. form driven) that doesn't know about specific resources such as procedure etc.</t>
+  </si>
+  <si>
+    <t>汎用的なケアプランシステム向けの簡易形式の詳細。 / Details in a simple form for generic care plan systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1157,16 +1159,16 @@
     <t>CarePlan.activity.detail.kind</t>
   </si>
   <si>
-    <t>Appointment | CommunicationRequest | DeviceRequest | MedicationRequest | NutritionOrder | Task | ServiceRequest | VisionPrescription</t>
-  </si>
-  <si>
-    <t>A description of the kind of resource the in-line definition of a care plan activity is representing.  The CarePlan.activity.detail is an in-line definition when a resource is not referenced using CarePlan.activity.reference.  For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest.</t>
-  </si>
-  <si>
-    <t>May determine what types of extensions are permitted.</t>
-  </si>
-  <si>
-    <t>Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
+    <t>予約 | コミュニケーションリクエスト | デバイスリクエスト | 薬剤リクエスト | 栄養指示 | タスク | サービスリクエスト | 視力処方箋 / Appointment | CommunicationRequest | DeviceRequest | MedicationRequest | NutritionOrder | Task | ServiceRequest | VisionPrescription</t>
+  </si>
+  <si>
+    <t>ケアプラン活動のインライン定義が表すリソースの種類を説明します。 CarePlan.activity.referenceを使用してリソースを参照しない場合、CarePlan.activity.detailはインライン定義です。例えば、MedicationRequest、ServiceRequest、またはCommunicationRequestです。 / A description of the kind of resource the in-line definition of a care plan activity is representing.  The CarePlan.activity.detail is an in-line definition when a resource is not referenced using CarePlan.activity.reference.  For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest.</t>
+  </si>
+  <si>
+    <t>どのタイプの拡張が許可されるかを決定する場合がある。 / May determine what types of extensions are permitted.</t>
+  </si>
+  <si>
+    <t>FHIRの一部として定義されたリソースタイプは、介護計画活動のインライン定義として表現できます。 / Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.3.0</t>
@@ -1182,34 +1184,34 @@
 </t>
   </si>
   <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
-  </si>
-  <si>
-    <t>Allows Questionnaires that the patient (or practitioner) should fill in to fulfill the care plan activity.</t>
+    <t>このCarePlan活動に完全または部分的に従われるFHIR定義プロトコル、ガイドライン、アンケート、またはその他の定義へのURL / The URL pointing to a FHIR-defined protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
+  </si>
+  <si>
+    <t>ケアプランのアクティビティを満たすために患者（または医療従事者）が記入すべき質問票を許可する。 / Allows Questionnaires that the patient (or practitioner) should fill in to fulfill the care plan activity.</t>
   </si>
   <si>
     <t>CarePlan.activity.detail.instantiatesUri</t>
   </si>
   <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
+    <t>このCarePlanアクティビティに部分的または完全に準拠されている外部に維持されたプロトコル、ガイドライン、アンケートまたはその他の定義を指すURL。 / The URL pointing to an externally maintained protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
   </si>
   <si>
     <t>CarePlan.activity.detail.code</t>
   </si>
   <si>
-    <t>Detail type of activity</t>
-  </si>
-  <si>
-    <t>Detailed description of the type of planned activity; e.g. what lab test, what procedure, what kind of encounter.</t>
-  </si>
-  <si>
-    <t>Tends to be less relevant for activities involving particular products.  Codes should not convey negation - use "prohibited" instead.</t>
-  </si>
-  <si>
-    <t>Allows matching performed to planned as well as validation against protocols.</t>
-  </si>
-  <si>
-    <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
+    <t>活動の詳細タイプ / Detail type of activity</t>
+  </si>
+  <si>
+    <t>計画された活動の詳細な説明；例えば、どのようなラボテスト、どのようなプロシジャー（処置等）、どのような受療行動か。 / Detailed description of the type of planned activity; e.g. what lab test, what procedure, what kind of encounter.</t>
+  </si>
+  <si>
+    <t>特定の製品に関する活動においては、あまり関係がない傾向があります。コードに否定を示すことは避け、代わりに「禁止」としてください。 / Tends to be less relevant for activities involving particular products.  Codes should not convey negation - use "prohibited" instead.</t>
+  </si>
+  <si>
+    <t>実施済みと計画済みの照合、およびプロトコルに対する検証を可能にする。 / Allows matching performed to planned as well as validation against protocols.</t>
+  </si>
+  <si>
+    <t>活動の種類に関する詳細な説明例：どのような実験、どのプロシジャー（処置等）、どのような受療行動ですか。 / Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/procedure-code|4.3.0</t>
@@ -1227,16 +1229,16 @@
     <t>CarePlan.activity.detail.reasonCode</t>
   </si>
   <si>
-    <t>Why activity should be done or why activity was prohibited</t>
-  </si>
-  <si>
-    <t>Provides the rationale that drove the inclusion of this particular activity as part of the plan or the reason why the activity was prohibited.</t>
-  </si>
-  <si>
-    <t>This could be a diagnosis code.  If a full condition record exists or additional detail is needed, use reasonCondition instead.</t>
-  </si>
-  <si>
-    <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
+    <t>なぜその活動を行うべきか、またはなぜその活動が禁止されたのか。 / Why activity should be done or why activity was prohibited</t>
+  </si>
+  <si>
+    <t>この特定の活動を計画の一部として含めることを推進した理論、または活動が禁止された理由を提供します。 / Provides the rationale that drove the inclusion of this particular activity as part of the plan or the reason why the activity was prohibited.</t>
+  </si>
+  <si>
+    <t>これは診断コードになる可能性があります。完全な状態記録が存在する場合や、追加の詳細が必要な場合は、reasonConditionを使用してください。 / This could be a diagnosis code.  If a full condition record exists or additional detail is needed, use reasonCondition instead.</t>
+  </si>
+  <si>
+    <t>看護計画のアクティビティが必要な理由を特定する。一般的な健康状態コード、予防、手術の準備などの概念を含めることができる。 / Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.3.0</t>
@@ -1252,44 +1254,45 @@
 </t>
   </si>
   <si>
-    <t>Why activity is needed</t>
-  </si>
-  <si>
-    <t>Indicates another resource, such as the health condition(s), whose existence justifies this request and drove the inclusion of this particular activity as part of the plan.</t>
-  </si>
-  <si>
-    <t>Conditions can be identified at the activity level that are not identified as reasons for the overall plan.</t>
+    <t>なぜ活動が必要なのか？ / Why activity is needed</t>
+  </si>
+  <si>
+    <t>健康状態など、このリクエストを正当化し、この特定のアクティビティを計画の一部として含める原動力となった他のリソースを示します。 / Indicates another resource, such as the health condition(s), whose existence justifies this request and drove the inclusion of this particular activity as part of the plan.</t>
+  </si>
+  <si>
+    <t>活動レベルで特定できる条件は、全体計画の理由として特定されないことがあります。 / Conditions can be identified at the activity level that are not identified as reasons for the overall plan.</t>
   </si>
   <si>
     <t>CarePlan.activity.detail.goal</t>
   </si>
   <si>
-    <t>Goals this activity relates to</t>
-  </si>
-  <si>
-    <t>Internal reference that identifies the goals that this activity is intended to contribute towards meeting.</t>
-  </si>
-  <si>
-    <t>So that participants know the link explicitly.</t>
+    <t>このアクティビティに関連する目標 / Goals this activity relates to</t>
+  </si>
+  <si>
+    <t>この活動に貢献することを目的とした目標を特定する内部参照。 / Internal reference that identifies the goals that this activity is intended to contribute towards meeting.</t>
+  </si>
+  <si>
+    <t>参加者がリンクを明示的に知ることができるようにするため。 / So that participants know the link explicitly.</t>
   </si>
   <si>
     <t>CarePlan.activity.detail.status</t>
   </si>
   <si>
-    <t>not-started | scheduled | in-progress | on-hold | completed | cancelled | stopped | unknown | entered-in-error</t>
-  </si>
-  <si>
-    <t>Identifies what progress is being made for the specific activity.</t>
-  </si>
-  <si>
-    <t>Some aspects of status can be inferred based on the resources linked in actionTaken.  Note that "status" is only as current as the plan was most recently updated.  
+    <t>未開始 | 予定済み | 進行中 | 保留中 | 完了 | 取り消し | 停止 | 不明 | エラーで入力済み / not-started | scheduled | in-progress | on-hold | completed | cancelled | stopped | unknown | entered-in-error</t>
+  </si>
+  <si>
+    <t>特定の活動に対して進捗状況を特定します。 / Identifies what progress is being made for the specific activity.</t>
+  </si>
+  <si>
+    <t>アクションを起こすためにリンクされているリソースに基づいて、ステータスの一部は推測できます。 "ステータス"は、計画が最後に更新された時点と同じくらい最新であることに注意してください。
+不明なコードは他のステータスを伝えるために使用されるべきではありません。不明なコードは、ステータスが適用される1つであるが、オーサリングシステムがアクティビティの現在の状態を知らない場合に使用する必要があります。 / Some aspects of status can be inferred based on the resources linked in actionTaken.  Note that "status" is only as current as the plan was most recently updated.  
 The unknown code is not to be used to convey other statuses.  The unknown code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the activity.</t>
   </si>
   <si>
-    <t>Indicates progress against the plan, whether the activity is still relevant for the plan.</t>
-  </si>
-  <si>
-    <t>Codes that reflect the current state of a care plan activity within its overall life cycle.</t>
+    <t>プランに対する進捗状況、アクティビティがプランにとってまだ関連があるかどうかを示す。 / Indicates progress against the plan, whether the activity is still relevant for the plan.</t>
+  </si>
+  <si>
+    <t>ケアプラン活動全体のライフサイクル内での現在の状態を反映するコード。 / Codes that reflect the current state of a care plan activity within its overall life cycle.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/care-plan-activity-status|4.3.0</t>
@@ -1307,13 +1310,13 @@
     <t>CarePlan.activity.detail.statusReason</t>
   </si>
   <si>
-    <t>Reason for current status</t>
-  </si>
-  <si>
-    <t>Provides reason why the activity isn't yet started, is on hold, was cancelled, etc.</t>
-  </si>
-  <si>
-    <t>Will generally not be present if status is "complete".  Be sure to prompt to update this (or at least remove the existing value) if the status is changed.</t>
+    <t>現在の状況の理由 / Reason for current status</t>
+  </si>
+  <si>
+    <t>活動がまだ開始されていない、保留中である、キャンセルされた理由を説明します。 / Provides reason why the activity isn't yet started, is on hold, was cancelled, etc.</t>
+  </si>
+  <si>
+    <t>完了」という状態の場合は一般に存在しないでしょう。状態が変更された場合に更新するように促すか、少なくとも既存の値を削除するようにしてください。 / Will generally not be present if status is "complete".  Be sure to prompt to update this (or at least remove the existing value) if the status is changed.</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -1326,19 +1329,19 @@
 </t>
   </si>
   <si>
-    <t>If true, activity is prohibiting action</t>
-  </si>
-  <si>
-    <t>If true, indicates that the described activity is one that must NOT be engaged in when following the plan.  If false, or missing, indicates that the described activity is one that should be engaged in when following the plan.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because it marks an activity as an activity that is not to be performed.</t>
-  </si>
-  <si>
-    <t>Captures intention to not do something that may have been previously typical.</t>
-  </si>
-  <si>
-    <t>If missing indicates that the described activity is one that should be engaged in when following the plan.</t>
+    <t>もしそれが真実なら、アクティビティは行動を妨げています。 / If true, activity is prohibiting action</t>
+  </si>
+  <si>
+    <t>真である場合、説明された活動が計画に従って行われてはならないものであることを示します。偽である場合、または欠落している場合、説明された活動が計画に従って行われるべきものであることを示します。 / If true, indicates that the described activity is one that must NOT be engaged in when following the plan.  If false, or missing, indicates that the described activity is one that should be engaged in when following the plan.</t>
+  </si>
+  <si>
+    <t>この要素は修飾子としてラベル付けされます。なぜなら、それは実行しない活動として活動をマークするからです。 / This element is labeled as a modifier because it marks an activity as an activity that is not to be performed.</t>
+  </si>
+  <si>
+    <t>以前は典型的であった可能性のあることを行わないという意図を記録する。 / Captures intention to not do something that may have been previously typical.</t>
+  </si>
+  <si>
+    <t>欠落している場合、記述されたアクティビティはプランに従う際に実施すべきものであることを示す。 / If missing indicates that the described activity is one that should be engaged in when following the plan.</t>
   </si>
   <si>
     <t>Request.doNotPerform</t>
@@ -1354,13 +1357,13 @@
 Periodstring</t>
   </si>
   <si>
-    <t>When activity is to occur</t>
-  </si>
-  <si>
-    <t>The period, timing or frequency upon which the described activity is to occur.</t>
-  </si>
-  <si>
-    <t>Allows prompting for activities and detection of missed planned activities.</t>
+    <t>活動が発生するとき / When activity is to occur</t>
+  </si>
+  <si>
+    <t>記述されたアクティビティが発生する期間、タイミング、または頻度。 / The period, timing or frequency upon which the described activity is to occur.</t>
+  </si>
+  <si>
+    <t>アクティビティの促進と、計画されたアクティビティの見逃しの検出を可能にする。 / Allows prompting for activities and detection of missed planned activities.</t>
   </si>
   <si>
     <t>TQ1</t>
@@ -1373,16 +1376,16 @@
 </t>
   </si>
   <si>
-    <t>Where it should happen</t>
-  </si>
-  <si>
-    <t>Identifies the facility where the activity will occur; e.g. home, hospital, specific clinic, etc.</t>
-  </si>
-  <si>
-    <t>May reference a specific clinical location or may identify a type of location.</t>
-  </si>
-  <si>
-    <t>Helps in planning of activity.</t>
+    <t>起こるべき場所はどこですか？ / Where it should happen</t>
+  </si>
+  <si>
+    <t>活動が行われる施設を特定します。例えば、自宅、病院、特定のクリニックなどです。 / Identifies the facility where the activity will occur; e.g. home, hospital, specific clinic, etc.</t>
+  </si>
+  <si>
+    <t>特定の臨床ロケーションを参照する場合もあれば、ロケーションのタイプを識別することもあります。 / May reference a specific clinical location or may identify a type of location.</t>
+  </si>
+  <si>
+    <t>アクティビティの計画に役立つ。 / Helps in planning of activity.</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role</t>
@@ -1398,13 +1401,13 @@
 </t>
   </si>
   <si>
-    <t>Who will be responsible?</t>
-  </si>
-  <si>
-    <t>Identifies who's expected to be involved in the activity.</t>
-  </si>
-  <si>
-    <t>A performer MAY also be a participant in the care plan.</t>
+    <t>誰が責任を負うのですか？ / Who will be responsible?</t>
+  </si>
+  <si>
+    <t>誰がその活動に関与する必要があるかを特定します。 / Identifies who's expected to be involved in the activity.</t>
+  </si>
+  <si>
+    <t>演者は介護プランの参加者である可能性もあります。 / A performer MAY also be a participant in the care plan.</t>
   </si>
   <si>
     <t>Request.performer</t>
@@ -1423,13 +1426,13 @@
 Reference(Substance|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication)</t>
   </si>
   <si>
-    <t>What is to be administered/supplied</t>
-  </si>
-  <si>
-    <t>Identifies the food, drug or other product to be consumed or supplied in the activity.</t>
-  </si>
-  <si>
-    <t>A product supplied or administered as part of a care plan activity.</t>
+    <t>何を管理/供給するのですか？ / What is to be administered/supplied</t>
+  </si>
+  <si>
+    <t>活動で消費または提供される食料品、薬品、またはその他の製品を識別します。 / Identifies the food, drug or other product to be consumed or supplied in the activity.</t>
+  </si>
+  <si>
+    <t>ケア・プランのアクティビティーの一環として提供される製品またはアレンジメント / A product supplied or administered as part of a care plan activity.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medication-codes|4.3.0</t>
@@ -1452,13 +1455,13 @@
 </t>
   </si>
   <si>
-    <t>How to consume/day?</t>
-  </si>
-  <si>
-    <t>Identifies the quantity expected to be consumed in a given day.</t>
-  </si>
-  <si>
-    <t>Allows rough dose checking.</t>
+    <t>「1日に何回飲むべきですか？」" / How to consume/day?</t>
+  </si>
+  <si>
+    <t>特定日に消費される予想数量を特定する。 / Identifies the quantity expected to be consumed in a given day.</t>
+  </si>
+  <si>
+    <t>おおよその用量チェックを可能にする。 / Allows rough dose checking.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP][classCode=SBADM].doseQuantity</t>
@@ -1470,10 +1473,10 @@
     <t>CarePlan.activity.detail.quantity</t>
   </si>
   <si>
-    <t>How much to administer/supply/consume</t>
-  </si>
-  <si>
-    <t>Identifies the quantity expected to be supplied, administered or consumed by the subject.</t>
+    <t>どのくらいの量を与える／支給する／消費するのですか？ / How much to administer/supply/consume</t>
+  </si>
+  <si>
+    <t>被験者によって供給、投与、消費される予定の数量を特定する。 / Identifies the quantity expected to be supplied, administered or consumed by the subject.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP][classCode=SPLY].quantity</t>
@@ -1485,10 +1488,10 @@
     <t>CarePlan.activity.detail.description</t>
   </si>
   <si>
-    <t>Extra info describing activity to perform</t>
-  </si>
-  <si>
-    <t>This provides a textual description of constraints on the intended activity occurrence, including relation to other activities.  It may also include objectives, pre-conditions and end-conditions.  Finally, it may convey specifics about the activity such as body site, method, route, etc.</t>
+    <t>実施するアクティビティを説明する追加情報 / Extra info describing activity to perform</t>
+  </si>
+  <si>
+    <t>これは意図された活動の発生に関する制約のテキスト上の説明を提供し、他の活動との関係を含むことがあります。また、目的、前提条件、終了条件も含まれる場合があります。最後に、場所、方法、経路などの活動に関する詳細を伝えることもできます。 / This provides a textual description of constraints on the intended activity occurrence, including relation to other activities.  It may also include objectives, pre-conditions and end-conditions.  Finally, it may convey specifics about the activity such as body site, method, route, etc.</t>
   </si>
   <si>
     <t>.text</t>
@@ -1497,13 +1500,13 @@
     <t>CarePlan.note</t>
   </si>
   <si>
-    <t>Comments about the plan</t>
-  </si>
-  <si>
-    <t>General notes about the care plan not covered elsewhere.</t>
-  </si>
-  <si>
-    <t>Used to capture information that applies to the plan as a whole that doesn't fit into discrete elements.</t>
+    <t>この計画に対するコメント / Comments about the plan</t>
+  </si>
+  <si>
+    <t>介護計画についてのその他の項目には含まれていない一般的な注意事項 / General notes about the care plan not covered elsewhere.</t>
+  </si>
+  <si>
+    <t>個別の要素に収まらない、プラン全体に適用される情報を記録するために使用される。 / Used to capture information that applies to the plan as a whole that doesn't fit into discrete elements.</t>
   </si>
   <si>
     <t>Request.note</t>
@@ -1837,7 +1840,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="136.375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="202.50390625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="48.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
